--- a/excel-model/sprint_analysis.xlsx
+++ b/excel-model/sprint_analysis.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,14 +12,14 @@
     <sheet name="Dashboard_Base" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +28,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -56,52 +66,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="009C0006"/>
-          <bgColor rgb="009C0006"/>
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
-          <bgColor rgb="00FFC7CE"/>
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFEB9C"/>
-          <bgColor rgb="00FFEB9C"/>
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
-          <bgColor rgb="00C6EFCE"/>
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00D9D9D9"/>
-          <bgColor rgb="00D9D9D9"/>
+          <fgColor rgb="FF9C0006"/>
+          <bgColor rgb="FF9C0006"/>
         </patternFill>
       </fill>
     </dxf>
@@ -200,7 +211,7 @@
     <tableColumn id="16" name="Completed_In_Sprint_Flag"/>
     <tableColumn id="17" name="Carry_Forward_Flag"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -494,7 +505,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -604,9 +615,6 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v/>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -746,17 +754,11 @@
           <t>01-01-2024</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v/>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v/>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -776,9 +778,6 @@
         <is>
           <t>14-01-2024</t>
         </is>
-      </c>
-      <c r="J4" t="n">
-        <v/>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -819,17 +818,11 @@
           <t>01-01-2024</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v/>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v/>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -849,9 +842,6 @@
         <is>
           <t>14-01-2024</t>
         </is>
-      </c>
-      <c r="J5" t="n">
-        <v/>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -892,17 +882,11 @@
           <t>02-01-2024</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v/>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v/>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -922,9 +906,6 @@
         <is>
           <t>14-01-2024</t>
         </is>
-      </c>
-      <c r="J6" t="n">
-        <v/>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -965,17 +946,11 @@
           <t>02-01-2024</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v/>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v/>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -995,9 +970,6 @@
         <is>
           <t>14-01-2024</t>
         </is>
-      </c>
-      <c r="J7" t="n">
-        <v/>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1038,9 +1010,6 @@
           <t>02-01-2024</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v/>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>asmith</t>
@@ -1070,9 +1039,6 @@
         <is>
           <t>14-01-2024</t>
         </is>
-      </c>
-      <c r="J8" t="n">
-        <v/>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1113,17 +1079,11 @@
           <t>02-01-2024</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v/>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v/>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -1143,9 +1103,6 @@
         <is>
           <t>14-01-2024</t>
         </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1196,9 +1153,6 @@
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v/>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -1338,17 +1292,11 @@
           <t>04-01-2024</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v/>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v/>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -1368,9 +1316,6 @@
         <is>
           <t>14-01-2024</t>
         </is>
-      </c>
-      <c r="J12" t="n">
-        <v/>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1488,9 +1433,6 @@
           <t>15-01-2024</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v/>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>rjones</t>
@@ -1520,9 +1462,6 @@
         <is>
           <t>28-01-2024</t>
         </is>
-      </c>
-      <c r="J14" t="n">
-        <v/>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1566,45 +1505,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="8.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.21875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="13.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="15.88671875" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="19.109375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.21875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15.77734375" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Sprint_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Total_Issues</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Planned_Work</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Completed_Work</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Completed_In_Sprint</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Spillover</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Validation_Check</t>
         </is>
       </c>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1680,35 +1629,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="8.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="20.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="17" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="24" bestFit="1" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Sprint_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Commitment_Reliability</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Spillover_Rate</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Risk_Severity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Data_Strength_Flag</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Adjusted_Risk_Label</t>
         </is>
@@ -1780,9 +1737,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="111.21875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="5" bestFit="1" customWidth="1" min="2" max="3"/>
+    <col width="24" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="23.5546875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14.5546875" bestFit="1" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ELITE ANALYTICS: DELIVERY RISK FRAMEWORK</t>
@@ -1874,9 +1838,10 @@
           <t>Worst Reliable Sprint</t>
         </is>
       </c>
-      <c r="G8">
-        <f>INDEX(Metrics_Calculation!A2:A3, MATCH(1, (Metrics_Calculation!B2:B3=MINIFS(Metrics_Calculation!B2:B3, Metrics_Calculation!E2:E3, "Reliable")) * (Metrics_Calculation!E2:E3="Reliable"), 0))</f>
-        <v/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sprint_01</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1945,19 +1910,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="4">
       <formula>SEARCH("Critical",D5)</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="3">
       <formula>SEARCH("High",D5)</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>SEARCH("Moderate",D5)</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>SEARCH("Low (",D5)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="0">
       <formula>SEARCH("Uncertain",D5)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/excel-model/sprint_analysis.xlsx
+++ b/excel-model/sprint_analysis.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +13,7 @@
     <sheet name="Dashboard_Base" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,22 +29,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
     </font>
   </fonts>
   <fills count="2">
@@ -73,46 +67,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
+          <fgColor rgb="009C0006"/>
+          <bgColor rgb="009C0006"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF9C0006"/>
-          <bgColor rgb="FF9C0006"/>
+          <fgColor rgb="00D9D9D9"/>
+          <bgColor rgb="00D9D9D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -211,7 +205,7 @@
     <tableColumn id="16" name="Completed_In_Sprint_Flag"/>
     <tableColumn id="17" name="Carry_Forward_Flag"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
 </table>
 </file>
 
@@ -505,7 +499,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -615,6 +609,9 @@
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v/>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -754,11 +751,17 @@
           <t>01-01-2024</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v/>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v/>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -778,6 +781,9 @@
         <is>
           <t>14-01-2024</t>
         </is>
+      </c>
+      <c r="J4" t="n">
+        <v/>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -818,11 +824,17 @@
           <t>01-01-2024</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v/>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v/>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -842,6 +854,9 @@
         <is>
           <t>14-01-2024</t>
         </is>
+      </c>
+      <c r="J5" t="n">
+        <v/>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -882,11 +897,17 @@
           <t>02-01-2024</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v/>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v/>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -906,6 +927,9 @@
         <is>
           <t>14-01-2024</t>
         </is>
+      </c>
+      <c r="J6" t="n">
+        <v/>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -946,11 +970,17 @@
           <t>02-01-2024</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v/>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v/>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -970,6 +1000,9 @@
         <is>
           <t>14-01-2024</t>
         </is>
+      </c>
+      <c r="J7" t="n">
+        <v/>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1010,6 +1043,9 @@
           <t>02-01-2024</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v/>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>asmith</t>
@@ -1039,6 +1075,9 @@
         <is>
           <t>14-01-2024</t>
         </is>
+      </c>
+      <c r="J8" t="n">
+        <v/>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1079,11 +1118,17 @@
           <t>02-01-2024</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v/>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v/>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -1103,6 +1148,9 @@
         <is>
           <t>14-01-2024</t>
         </is>
+      </c>
+      <c r="J9" t="n">
+        <v/>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1153,6 +1201,9 @@
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -1292,11 +1343,17 @@
           <t>04-01-2024</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v/>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Unassigned</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v/>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>GitHub</t>
@@ -1316,6 +1373,9 @@
         <is>
           <t>14-01-2024</t>
         </is>
+      </c>
+      <c r="J12" t="n">
+        <v/>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1433,6 +1493,9 @@
           <t>15-01-2024</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v/>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>rjones</t>
@@ -1462,6 +1525,9 @@
         <is>
           <t>28-01-2024</t>
         </is>
+      </c>
+      <c r="J14" t="n">
+        <v/>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1505,55 +1571,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="8.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="13.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="15.88671875" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.109375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="8.21875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.77734375" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sprint_ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total_Issues</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Planned_Work</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Completed_Work</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Completed_In_Sprint</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spillover</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Validation_Check</t>
         </is>
       </c>
-      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1629,43 +1685,35 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="8.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="20.77734375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="12.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="17" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="24" bestFit="1" customWidth="1" min="6" max="6"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sprint_ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Commitment_Reliability</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Spillover_Rate</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Risk_Severity</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Data_Strength_Flag</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Data_Confidence</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Adjusted_Risk_Label</t>
         </is>
@@ -1690,11 +1738,11 @@
         <v/>
       </c>
       <c r="E2">
-        <f>IF(Sprint_Summary!C2&lt;5, "Low Confidence", "Reliable")</f>
+        <f>IF(Sprint_Summary!C2&lt;5, "Low Confidence", "High Confidence")</f>
         <v/>
       </c>
       <c r="F2">
-        <f>IF(E2="Low Confidence", "Uncertain (Low Confidence)", D2 &amp; " (High Confidence)")</f>
+        <f>IF(E2="Low Confidence", "Uncertain — Low Confidence", D2 &amp; " — High Confidence")</f>
         <v/>
       </c>
     </row>
@@ -1717,11 +1765,11 @@
         <v/>
       </c>
       <c r="E3">
-        <f>IF(Sprint_Summary!C3&lt;5, "Low Confidence", "Reliable")</f>
+        <f>IF(Sprint_Summary!C3&lt;5, "Low Confidence", "High Confidence")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>IF(E3="Low Confidence", "Uncertain (Low Confidence)", D3 &amp; " (High Confidence)")</f>
+        <f>IF(E3="Low Confidence", "Uncertain — Low Confidence", D3 &amp; " — High Confidence")</f>
         <v/>
       </c>
     </row>
@@ -1736,20 +1784,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="111.21875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="5" bestFit="1" customWidth="1" min="2" max="3"/>
-    <col width="24" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="23.5546875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="14.5546875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ELITE ANALYTICS: DELIVERY RISK FRAMEWORK</t>
+          <t>Agile Delivery Risk Analysis — Sprint Predictability Assessment</t>
         </is>
       </c>
     </row>
@@ -1783,13 +1832,13 @@
         <f>Metrics_Calculation!F2</f>
         <v/>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Weighted Avg Commitment</t>
-        </is>
-      </c>
-      <c r="G5">
-        <f>ROUND(SUMIFS(Sprint_Summary!E2:E3, Metrics_Calculation!E2:E3, "Reliable") / MAX(1, SUMIFS(Sprint_Summary!C2:C3, Metrics_Calculation!E2:E3, "Reliable")), 2)</f>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Weighted Avg Commitment Reliability</t>
+        </is>
+      </c>
+      <c r="G5" s="2">
+        <f>ROUND(SUMIFS(Sprint_Summary!E2:E3, Metrics_Calculation!E2:E3, "High Confidence") / MAX(1, SUMIFS(Sprint_Summary!C2:C3, Metrics_Calculation!E2:E3, "High Confidence")), 2)</f>
         <v/>
       </c>
     </row>
@@ -1811,13 +1860,13 @@
         <f>Metrics_Calculation!F3</f>
         <v/>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Weighted Avg Spillover</t>
-        </is>
-      </c>
-      <c r="G6">
-        <f>ROUND(SUMIFS(Sprint_Summary!F2:F3, Metrics_Calculation!E2:E3, "Reliable") / MAX(1, SUMIFS(Sprint_Summary!B2:B3, Metrics_Calculation!E2:E3, "Reliable")), 2)</f>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Weighted Avg Spillover Rate</t>
+        </is>
+      </c>
+      <c r="G6" s="2">
+        <f>ROUND(SUMIFS(Sprint_Summary!F2:F3, Metrics_Calculation!E2:E3, "High Confidence") / MAX(1, SUMIFS(Sprint_Summary!B2:B3, Metrics_Calculation!E2:E3, "High Confidence")), 2)</f>
         <v/>
       </c>
     </row>
@@ -1828,7 +1877,7 @@
         </is>
       </c>
       <c r="G7">
-        <f>COUNTIFS(Metrics_Calculation!E2:E3, "Reliable", Metrics_Calculation!D2:D3, "Critical")</f>
+        <f>COUNTIFS(Metrics_Calculation!E2:E3, "High Confidence", Metrics_Calculation!D2:D3, "Critical")</f>
         <v/>
       </c>
     </row>
@@ -1851,7 +1900,7 @@
         </is>
       </c>
       <c r="G9">
-        <f>IF(COUNTIF(Metrics_Calculation!E2:E3, "Reliable")&lt;3, "Insufficient Data", "Requires Analysis")</f>
+        <f>IF(COUNTIF(Metrics_Calculation!E2:E3, "High Confidence")&lt;3, "Insufficient Data", "Stable")</f>
         <v/>
       </c>
     </row>
@@ -1866,63 +1915,70 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Key Insight:</t>
+    <row r="12">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Only 3 out of 12 planned tasks were delivered within sprint, reflecting a 75% execution gap.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Reliable sprint data indicates critically low delivery predictability, suggesting systemic overcommitment and poor execution discipline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Recommended Actions:</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Key Analytical Insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Reliable sprint data shows only 25% commitment fulfillment, indicating severe overcommitment and execution inefficiency within sprint cycles.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>* Reduce sprint scope by 20–30%</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Recommended Business Actions</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>* Limit concurrent work (WIP)</t>
+          <t>* Reduce sprint commitment volume by ~75% (based on current 25% completion rate)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>* Introduce mid-sprint progress tracking</t>
+          <t>* Limit active work items to align with observed completion capacity (3 of 12 tasks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>* Implement mid-sprint checkpoint reviews to prevent late-stage spillovers</t>
         </is>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" priority="1" dxfId="4">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>SEARCH("Critical",D5)</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="3">
-      <formula>SEARCH("High",D5)</formula>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>SEARCH("High —",D5)</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>SEARCH("Moderate",D5)</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>SEARCH("Low (",D5)</formula>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>SEARCH("Low —",D5)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="0">
+    <cfRule type="expression" priority="5" dxfId="4">
       <formula>SEARCH("Uncertain",D5)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/excel-model/sprint_analysis.xlsx
+++ b/excel-model/sprint_analysis.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chiranjeevi PK\Desktop\Projects\Business Analyst\agile-delivery-risk-analytics\excel-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66549139-A03E-4491-AB5A-745D1DA91550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD653B4-DBE9-4CF6-9BE2-F7BF6A8ECD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint_Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Metrics_Calculation" sheetId="3" r:id="rId3"/>
     <sheet name="Dashboard_Base" sheetId="4" r:id="rId4"/>
+    <sheet name="Risk_Model" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="98">
   <si>
     <t>Issue_ID</t>
   </si>
@@ -87,6 +88,12 @@
     <t>Carry_Forward_Flag</t>
   </si>
   <si>
+    <t>Mid_Sprint_Date</t>
+  </si>
+  <si>
+    <t>Work_Started_Flag</t>
+  </si>
+  <si>
     <t>36279</t>
   </si>
   <si>
@@ -114,6 +121,9 @@
     <t>Valid</t>
   </si>
   <si>
+    <t>04-01-2024</t>
+  </si>
+  <si>
     <t>KAFKA-101</t>
   </si>
   <si>
@@ -183,9 +193,6 @@
     <t>36315</t>
   </si>
   <si>
-    <t>04-01-2024</t>
-  </si>
-  <si>
     <t>KAFKA-104</t>
   </si>
   <si>
@@ -210,6 +217,9 @@
     <t>28-01-2024</t>
   </si>
   <si>
+    <t>18-01-2024</t>
+  </si>
+  <si>
     <t>Total_Issues</t>
   </si>
   <si>
@@ -289,6 +299,36 @@
   </si>
   <si>
     <t>* Implement mid-sprint checkpoint reviews to prevent late-stage spillovers</t>
+  </si>
+  <si>
+    <t>Actual_Progress_Day3</t>
+  </si>
+  <si>
+    <t>Expected_Progress_Day3</t>
+  </si>
+  <si>
+    <t>Risk_Score</t>
+  </si>
+  <si>
+    <t>Predicted_Risk</t>
+  </si>
+  <si>
+    <t>Adjusted_Risk</t>
+  </si>
+  <si>
+    <t>Actual_Risk</t>
+  </si>
+  <si>
+    <t>Prediction_Accuracy</t>
+  </si>
+  <si>
+    <t>High Risk</t>
+  </si>
+  <si>
+    <t>Uncertain — Low Confidence</t>
+  </si>
+  <si>
+    <t>Correct</t>
   </si>
 </sst>
 </file>
@@ -723,13 +763,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="17" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -781,566 +821,638 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="L2" t="s">
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
         <v>24</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
       </c>
       <c r="J3">
         <v>4.21</v>
       </c>
       <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="L3" t="s">
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
         <v>24</v>
       </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>28</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>28</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J10">
         <v>0.41</v>
       </c>
       <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
         <v>23</v>
       </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J11">
         <v>12.12</v>
       </c>
       <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>28</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
         <v>23</v>
       </c>
-      <c r="L11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>20</v>
       </c>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K12" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
+        <v>28</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
         <v>32</v>
       </c>
-      <c r="L12" t="s">
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s">
         <v>24</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" t="s">
-        <v>22</v>
       </c>
       <c r="J13">
         <v>2.08</v>
       </c>
       <c r="K13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -1351,43 +1463,49 @@
       <c r="Q13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" t="s">
+        <v>28</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O14">
         <v>1</v>
@@ -1397,6 +1515,12 @@
       </c>
       <c r="Q14">
         <v>0</v>
+      </c>
+      <c r="R14" t="s">
+        <v>60</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1426,28 +1550,28 @@
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <f>COUNTIF(tbl_issues[Sprint_ID], A2)</f>
@@ -1476,7 +1600,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <f>COUNTIF(tbl_issues[Sprint_ID], A3)</f>
@@ -1510,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
@@ -1526,25 +1650,25 @@
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <f>ROUND(IF(Sprint_Summary!C2=0, 0, Sprint_Summary!E2/Sprint_Summary!C2), 2)</f>
@@ -1569,7 +1693,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <f>ROUND(IF(Sprint_Summary!C3=0, 0, Sprint_Summary!E3/Sprint_Summary!C3), 2)</f>
@@ -1590,6 +1714,12 @@
       <c r="F3" t="str">
         <f>IF(E3="Low Confidence", "Uncertain — Low Confidence", D3 &amp; " — High Confidence")</f>
         <v>Uncertain — Low Confidence</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <f>AVERAGE(B2:B3)</f>
+        <v>0.125</v>
       </c>
     </row>
   </sheetData>
@@ -1610,22 +1740,22 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <f>ROUND(Metrics_Calculation!B2, 2)</f>
@@ -1640,7 +1770,7 @@
         <v>Critical — High Confidence</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G5" s="2">
         <f>ROUND(SUMIFS(Sprint_Summary!E2:E3, Metrics_Calculation!E2:E3, "High Confidence") / MAX(1, SUMIFS(Sprint_Summary!C2:C3, Metrics_Calculation!E2:E3, "High Confidence")), 2)</f>
@@ -1649,7 +1779,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6">
         <f>ROUND(Metrics_Calculation!B3, 2)</f>
@@ -1664,7 +1794,7 @@
         <v>Uncertain — Low Confidence</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G6" s="2">
         <f>ROUND(SUMIFS(Sprint_Summary!F2:F3, Metrics_Calculation!E2:E3, "High Confidence") / MAX(1, SUMIFS(Sprint_Summary!B2:B3, Metrics_Calculation!E2:E3, "High Confidence")), 2)</f>
@@ -1673,7 +1803,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <f>COUNTIFS(Metrics_Calculation!E2:E3, "High Confidence", Metrics_Calculation!D2:D3, "Critical")</f>
@@ -1682,15 +1812,15 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G9" t="str">
         <f>IF(COUNTIF(Metrics_Calculation!E2:E3, "High Confidence")&lt;3, "Insufficient Data", "Stable")</f>
@@ -1699,7 +1829,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G10">
         <f>COUNTIF(Sprint_Summary!G2:G3, "Error")</f>
@@ -1708,37 +1838,37 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F12" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1761,4 +1891,113 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>999</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>999</v>
+      </c>
+      <c r="F3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/excel-model/sprint_analysis.xlsx
+++ b/excel-model/sprint_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chiranjeevi PK\Desktop\Projects\Business Analyst\agile-delivery-risk-analytics\excel-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD653B4-DBE9-4CF6-9BE2-F7BF6A8ECD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83098CA-EEE2-4F2B-ACE5-E2D3F05A8E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,7 @@
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint_Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Metrics_Calculation" sheetId="3" r:id="rId3"/>
-    <sheet name="Dashboard_Base" sheetId="4" r:id="rId4"/>
-    <sheet name="Risk_Model" sheetId="5" r:id="rId5"/>
+    <sheet name="Risk_Model" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="82">
   <si>
     <t>Issue_ID</t>
   </si>
@@ -251,54 +250,6 @@
   </si>
   <si>
     <t>Adjusted_Risk_Label</t>
-  </si>
-  <si>
-    <t>Agile Delivery Risk Analysis — Sprint Predictability Assessment</t>
-  </si>
-  <si>
-    <t>Sprint Performance Table</t>
-  </si>
-  <si>
-    <t>Executive Summary</t>
-  </si>
-  <si>
-    <t>Weighted Avg Commitment Reliability</t>
-  </si>
-  <si>
-    <t>Weighted Avg Spillover Rate</t>
-  </si>
-  <si>
-    <t>High Risk Sprint Count</t>
-  </si>
-  <si>
-    <t>Worst Reliable Sprint</t>
-  </si>
-  <si>
-    <t>Trend (Reliable Data Only)</t>
-  </si>
-  <si>
-    <t>Error Count</t>
-  </si>
-  <si>
-    <t>Only 3 out of 12 planned tasks were delivered within sprint, reflecting a 75% execution gap.</t>
-  </si>
-  <si>
-    <t>Key Analytical Insight</t>
-  </si>
-  <si>
-    <t>Reliable sprint data shows only 25% commitment fulfillment, indicating severe overcommitment and execution inefficiency within sprint cycles.</t>
-  </si>
-  <si>
-    <t>Recommended Business Actions</t>
-  </si>
-  <si>
-    <t>* Reduce sprint commitment volume by ~75% (based on current 25% completion rate)</t>
-  </si>
-  <si>
-    <t>* Limit active work items to align with observed completion capacity (3 of 12 tasks)</t>
-  </si>
-  <si>
-    <t>* Implement mid-sprint checkpoint reviews to prevent late-stage spillovers</t>
   </si>
   <si>
     <t>Actual_Progress_Day3</t>
@@ -335,29 +286,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -391,55 +326,14 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9C0006"/>
-          <bgColor rgb="FF9C0006"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1546,28 +1440,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="4"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -1646,25 +1540,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="4"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -1728,174 +1622,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="6" max="6" width="76.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
-        <f>ROUND(Metrics_Calculation!B2, 2)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C5">
-        <f>ROUND(Metrics_Calculation!C2, 2)</f>
-        <v>0.08</v>
-      </c>
-      <c r="D5" t="str">
-        <f>Metrics_Calculation!F2</f>
-        <v>Critical — High Confidence</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="2">
-        <f>ROUND(SUMIFS(Sprint_Summary!E2:E3, Metrics_Calculation!E2:E3, "High Confidence") / MAX(1, SUMIFS(Sprint_Summary!C2:C3, Metrics_Calculation!E2:E3, "High Confidence")), 2)</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6">
-        <f>ROUND(Metrics_Calculation!B3, 2)</f>
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <f>ROUND(Metrics_Calculation!C3, 2)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" t="str">
-        <f>Metrics_Calculation!F3</f>
-        <v>Uncertain — Low Confidence</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2">
-        <f>ROUND(SUMIFS(Sprint_Summary!F2:F3, Metrics_Calculation!E2:E3, "High Confidence") / MAX(1, SUMIFS(Sprint_Summary!B2:B3, Metrics_Calculation!E2:E3, "High Confidence")), 2)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7">
-        <f>COUNTIFS(Metrics_Calculation!E2:E3, "High Confidence", Metrics_Calculation!D2:D3, "Critical")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" t="str">
-        <f>IF(COUNTIF(Metrics_Calculation!E2:E3, "High Confidence")&lt;3, "Insufficient Data", "Stable")</f>
-        <v>Insufficient Data</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10">
-        <f>COUNTIF(Sprint_Summary!G2:G3, "Error")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F12" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D5:D6">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>SEARCH("Critical",D5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>SEARCH("High —",D5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>SEARCH("Moderate",D5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>SEARCH("Low —",D5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>SEARCH("Uncertain",D5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
@@ -1909,94 +1637,94 @@
     <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
         <v>11</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
         <v>999</v>
       </c>
-      <c r="F2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="F2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
         <v>999</v>
       </c>
-      <c r="F3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" t="s">
-        <v>97</v>
-      </c>
-    </row>
+      <c r="F3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
